--- a/Backlog - aplikacja nieobecnosci.xlsx
+++ b/Backlog - aplikacja nieobecnosci.xlsx
@@ -1225,7 +1225,7 @@
     <t>NFR-6</t>
   </si>
   <si>
-    <t>ODSTĘPSTWO — zakres zawężony do desktopu (decyzja 07.08.2026); wymaga potwierdzenia zamawiającego</t>
+    <t>Zrealizowane w wariancie uzgodnionym — pulpit i wpis mobilnie, pozostałe ekrany desktop; zawężenie zatwierdzone przez zamawiającego 10.08.2026</t>
   </si>
   <si>
     <t>US-N7</t>
@@ -1243,7 +1243,7 @@
     <t>NFR-7</t>
   </si>
   <si>
-    <t>Zrealizowane z zawężeniem — audyt axe 10.08.2026: 0 naruszeń na 12 ekranach; wyłączone 1.4.10 Reflow, wymaga potwierdzenia zamawiającego</t>
+    <t>Zrealizowane — audyt axe 10.08.2026: 0 naruszeń na 12 ekranach; wyłączenie 1.4.10 Reflow zatwierdzone przez zamawiającego 10.08.2026</t>
   </si>
   <si>
     <t>US-N8</t>
@@ -1448,10 +1448,10 @@
     <t>Funkcja działa w aplikacji; pokryta testami silnika lub suitą integracyjną.</t>
   </si>
   <si>
-    <t>Stan wdrożenia — ODSTĘPSTWO</t>
-  </si>
-  <si>
-    <t>Zakres świadomie zawężony w stosunku do wymagania. Wymaga potwierdzenia zamawiającego.</t>
+    <t>Stan wdrożenia — wariant uzgodniony</t>
+  </si>
+  <si>
+    <t>Zakres zawężony w stosunku do pierwotnego brzmienia wymagania i zatwierdzony przez zamawiającego. Nie jest długiem ani odstępstwem do domknięcia.</t>
   </si>
   <si>
     <t>Stan wdrożenia — Niezrealizowane</t>

--- a/Backlog - aplikacja nieobecnosci.xlsx
+++ b/Backlog - aplikacja nieobecnosci.xlsx
@@ -1,78 +1,84 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Backlog" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Epiki" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Legenda" state="visible" r:id="rId6"/>
+    <sheet name="Backlog" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Epiki" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Legenda" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="456">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Typ zgłoszenia</t>
-  </si>
-  <si>
-    <t>Epik ID</t>
-  </si>
-  <si>
-    <t>Epik</t>
-  </si>
-  <si>
-    <t>Podsumowanie</t>
-  </si>
-  <si>
-    <t>Opis (Jako / Chcę / Aby)</t>
-  </si>
-  <si>
-    <t>Kryteria akceptacji</t>
-  </si>
-  <si>
-    <t>Priorytet</t>
-  </si>
-  <si>
-    <t>Story points</t>
-  </si>
-  <si>
-    <t>Faza</t>
-  </si>
-  <si>
-    <t>Ref. FR/NFR</t>
-  </si>
-  <si>
-    <t>Stan wdrożenia</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>Rejestracja i zarządzanie nieobecnościami</t>
-  </si>
-  <si>
-    <t>Pracownicy samodzielnie wpisują i edytują nieobecności bez blokad pliku.</t>
-  </si>
-  <si>
-    <t>US-A1</t>
-  </si>
-  <si>
-    <t>Historyjka</t>
-  </si>
-  <si>
-    <t>Samoobsługowy wpis nieobecności</t>
-  </si>
-  <si>
-    <t>Jako pracownik (UoP/B2B/OUT) chcę wpisać własną nieobecność (typ, data od–do), aby zaplanować dni wolne bez plików Excel.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="464">
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typ zgłoszenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epik ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podsumowanie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opis (Jako / Chcę / Aby)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kryteria akceptacji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorytet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ref. FR/NFR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stan wdrożenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejestracja i zarządzanie nieobecnościami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pracownicy samodzielnie wpisują i edytują nieobecności bez blokad pliku.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historyjka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samoobsługowy wpis nieobecności</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik (UoP/B2B/OUT) chcę wpisać własną nieobecność (typ, data od–do), aby zaplanować dni wolne bez plików Excel.</t>
   </si>
   <si>
     <t xml:space="preserve">• Formularz dostępny po zalogowaniu
@@ -80,25 +86,25 @@
 • Wpis zapisywany i widoczny natychmiast</t>
   </si>
   <si>
-    <t>Must</t>
-  </si>
-  <si>
-    <t>MVP</t>
-  </si>
-  <si>
-    <t>FR-A1</t>
-  </si>
-  <si>
-    <t>Zrealizowane</t>
-  </si>
-  <si>
-    <t>US-A2</t>
-  </si>
-  <si>
-    <t>Wpis przez zakres dat z pomijaniem weekendów i świąt</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę podać zakres dat i mieć policzone tylko dni robocze, aby nie liczyć ręcznie weekendów i świąt.</t>
+    <t xml:space="preserve">Must</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MVP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wpis przez zakres dat z pomijaniem weekendów i świąt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę podać zakres dat i mieć policzone tylko dni robocze, aby nie liczyć ręcznie weekendów i świąt.</t>
   </si>
   <si>
     <t xml:space="preserve">• Weekendy nie są naliczane
@@ -106,86 +112,86 @@
 • Liczba dni roboczych pokazana przed zapisem</t>
   </si>
   <si>
-    <t>FR-A2</t>
-  </si>
-  <si>
-    <t>US-A3</t>
-  </si>
-  <si>
-    <t>Obsługa niepełnych dni (pół dnia / godziny)</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę wpisać pół dnia (AM/PM) lub konkretne godziny, aby odwzorować krótsze nieobecności w systemie 8-godzinnym.</t>
+    <t xml:space="preserve">FR-A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obsługa niepełnych dni (pół dnia / godziny)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę wpisać pół dnia (AM/PM) lub konkretne godziny, aby odwzorować krótsze nieobecności w systemie 8-godzinnym.</t>
   </si>
   <si>
     <t xml:space="preserve">• Wybór AM/PM lub zakresu godzin
 • Przeliczenie na ułamek dnia w balansie i capacity</t>
   </si>
   <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Faza 2</t>
-  </si>
-  <si>
-    <t>FR-A3</t>
-  </si>
-  <si>
-    <t>US-A4</t>
-  </si>
-  <si>
-    <t>Edycja i usuwanie własnych wpisów</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę edytować lub usunąć swój wpis, aby poprawić pomyłkę bez udziału innych.</t>
+    <t xml:space="preserve">Should</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faza 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edycja i usuwanie własnych wpisów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę edytować lub usunąć swój wpis, aby poprawić pomyłkę bez udziału innych.</t>
   </si>
   <si>
     <t xml:space="preserve">• Edycja/usuwanie tylko własnych wpisów
 • Balans i capacity aktualizują się &lt; 1 s</t>
   </si>
   <si>
-    <t>FR-A4</t>
-  </si>
-  <si>
-    <t>US-A5</t>
-  </si>
-  <si>
-    <t>Korekta wpisów zespołu przez lidera</t>
-  </si>
-  <si>
-    <t>Jako lider chcę poprawić wpis członka zespołu na etapie weryfikacji, aby skorygować błędy bez czekania na pracownika.</t>
+    <t xml:space="preserve">FR-A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korekta wpisów zespołu przez lidera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider chcę poprawić wpis członka zespołu na etapie weryfikacji, aby skorygować błędy bez czekania na pracownika.</t>
   </si>
   <si>
     <t xml:space="preserve">• Lider edytuje wpisy tylko w swoim zespole
 • Zmiana odnotowana w historii (FR-I1)</t>
   </si>
   <si>
-    <t>FR-A5</t>
-  </si>
-  <si>
-    <t>US-A6</t>
-  </si>
-  <si>
-    <t>Wielodostęp w czasie rzeczywistym</t>
-  </si>
-  <si>
-    <t>Jako zespół chcę wpisywać nieobecności równocześnie z innymi, aby uniknąć blokad i „kolejek” znanych z Excela.</t>
+    <t xml:space="preserve">FR-A5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wielodostęp w czasie rzeczywistym</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako zespół chcę wpisywać nieobecności równocześnie z innymi, aby uniknąć blokad i „kolejek” znanych z Excela.</t>
   </si>
   <si>
     <t xml:space="preserve">• Brak blokad typu check-out
 • Równoczesne zapisy nie powodują utraty danych ani konfliktów</t>
   </si>
   <si>
-    <t>FR-A6</t>
-  </si>
-  <si>
-    <t>US-A7</t>
-  </si>
-  <si>
-    <t>Walidacja wpisu</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę otrzymać czytelny komunikat przy błędnym wpisie, aby uniknąć przekroczenia puli i kolizji.</t>
+    <t xml:space="preserve">FR-A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walidacja wpisu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę otrzymać czytelny komunikat przy błędnym wpisie, aby uniknąć przekroczenia puli i kolizji.</t>
   </si>
   <si>
     <t xml:space="preserve">• Kontrola przekroczenia puli, kolizji i zakresu dat
@@ -193,32 +199,32 @@
 • Komunikat wskazuje konkretny problem</t>
   </si>
   <si>
-    <t>FR-A7</t>
-  </si>
-  <si>
-    <t>US-A8</t>
-  </si>
-  <si>
-    <t>Wybór typu nieobecności z listy</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę wybrać typ nieobecności z listy administratora, aby umożliwić właściwe wyliczenia (np. L4).</t>
+    <t xml:space="preserve">FR-A7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wybór typu nieobecności z listy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę wybrać typ nieobecności z listy administratora, aby umożliwić właściwe wyliczenia (np. L4).</t>
   </si>
   <si>
     <t xml:space="preserve">• Lista typów konfigurowalna przez admina
 • Prezentacja w UI jednolita niezależnie od typu (D1)</t>
   </si>
   <si>
-    <t>FR-A8</t>
-  </si>
-  <si>
-    <t>US-A9</t>
-  </si>
-  <si>
-    <t>Proaktywna asysta przy wpisie</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę widzieć dostępny balans i kolizje przed zapisem, aby ograniczyć liczbę błędnych wpisów.</t>
+    <t xml:space="preserve">FR-A8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proaktywna asysta przy wpisie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę widzieć dostępny balans i kolizje przed zapisem, aby ograniczyć liczbę błędnych wpisów.</t>
   </si>
   <si>
     <t xml:space="preserve">• Dostępny balans i skutek wpisu widoczne na żywo
@@ -226,63 +232,63 @@
 • Ostrzeżenie o kolizji przed zapisem</t>
   </si>
   <si>
-    <t>FR-A9</t>
-  </si>
-  <si>
-    <t>US-A10</t>
-  </si>
-  <si>
-    <t>Operacje masowe</t>
-  </si>
-  <si>
-    <t>Jako lider / administrator chcę wpisać nieobecność dla wielu osób naraz, aby obsłużyć np. wyjazd całego squadu jednym działaniem.</t>
+    <t xml:space="preserve">FR-A9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operacje masowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider / administrator chcę wpisać nieobecność dla wielu osób naraz, aby obsłużyć np. wyjazd całego squadu jednym działaniem.</t>
   </si>
   <si>
     <t xml:space="preserve">• Jeden formularz tworzy wpisy dla wielu osób
 • Walidacja wykonywana per osoba</t>
   </si>
   <si>
-    <t>Could</t>
-  </si>
-  <si>
-    <t>Faza 3</t>
-  </si>
-  <si>
-    <t>FR-A10</t>
-  </si>
-  <si>
-    <t>US-A11</t>
-  </si>
-  <si>
-    <t>Potwierdzenia i cofanie operacji</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę potwierdzać usuwanie i móc cofnąć ostatnią operację, aby uniknąć przypadkowej utraty wpisu.</t>
+    <t xml:space="preserve">Could</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faza 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-A10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-A11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potwierdzenia i cofanie operacji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę potwierdzać usuwanie i móc cofnąć ostatnią operację, aby uniknąć przypadkowej utraty wpisu.</t>
   </si>
   <si>
     <t xml:space="preserve">• Usunięcie wymaga potwierdzenia
 • Funkcja „cofnij” przywraca wpis i balans</t>
   </si>
   <si>
-    <t>FR-A11</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>Wyliczenia, pula i balans</t>
-  </si>
-  <si>
-    <t>Poprawne, odrębne liczenie urlopu dla UoP i B2B/OUT wraz z przypadkami brzegowymi.</t>
-  </si>
-  <si>
-    <t>US-B1</t>
-  </si>
-  <si>
-    <t>Odrębne reguły liczenia UoP vs B2B/OUT</t>
-  </si>
-  <si>
-    <t>Jako system chcę liczyć dni wg roku kalendarzowego (UoP) i budżetowego (B2B/OUT), aby zapewnić poprawne salda dla obu form (warunek akceptacji).</t>
+    <t xml:space="preserve">FR-A11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyliczenia, pula i balans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poprawne, odrębne liczenie urlopu dla UoP i B2B/OUT wraz z przypadkami brzegowymi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odrębne reguły liczenia UoP vs B2B/OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako system chcę liczyć dni wg roku kalendarzowego (UoP) i budżetowego (B2B/OUT), aby zapewnić poprawne salda dla obu form (warunek akceptacji).</t>
   </si>
   <si>
     <t xml:space="preserve">• UoP rozliczany w roku kalendarzowym
@@ -290,96 +296,96 @@
 • Właściwy okres dobierany wg formy zatrudnienia</t>
   </si>
   <si>
-    <t>FR-B1</t>
-  </si>
-  <si>
-    <t>US-B2</t>
-  </si>
-  <si>
-    <t>Licznik na żywo: pula / wykorzystano / pozostało</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę widzieć aktualny licznik wykorzystania, aby wiedzieć ile dni zostało do rozplanowania.</t>
+    <t xml:space="preserve">FR-B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licznik na żywo: pula / wykorzystano / pozostało</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę widzieć aktualny licznik wykorzystania, aby wiedzieć ile dni zostało do rozplanowania.</t>
   </si>
   <si>
     <t xml:space="preserve">• Trzy wartości: pula, wykorzystano, pozostało
 • Aktualizacja &lt; 1 s po zmianie wpisu</t>
   </si>
   <si>
-    <t>FR-B2</t>
-  </si>
-  <si>
-    <t>US-B3</t>
-  </si>
-  <si>
-    <t>Pula urlopu: globalna + korekta indywidualna</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę ustawić pulę globalnie i korygować ją per osoba, aby zarządzać limitami bez integracji z TETA.</t>
+    <t xml:space="preserve">FR-B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pula urlopu: globalna + korekta indywidualna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę ustawić pulę globalnie i korygować ją per osoba, aby zarządzać limitami bez integracji z TETA.</t>
   </si>
   <si>
     <t xml:space="preserve">• Pula globalna propaguje się do pracowników
 • Korekta indywidualna nadpisuje wartość globalną</t>
   </si>
   <si>
-    <t>FR-B3</t>
-  </si>
-  <si>
-    <t>US-B4</t>
-  </si>
-  <si>
-    <t>Urlop zaległy i minimum do pozostawienia</t>
-  </si>
-  <si>
-    <t>Jako pracownik (UoP) chcę widzieć urlop zaległy i minimum do pozostawienia, aby planować wykorzystanie zgodnie z zasadami.</t>
+    <t xml:space="preserve">FR-B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urlop zaległy i minimum do pozostawienia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik (UoP) chcę widzieć urlop zaległy i minimum do pozostawienia, aby planować wykorzystanie zgodnie z zasadami.</t>
   </si>
   <si>
     <t xml:space="preserve">• Balans uwzględnia urlop zaległy
 • Minimum do pozostawienia wyróżnione</t>
   </si>
   <si>
-    <t>FR-B4</t>
-  </si>
-  <si>
-    <t>US-B5</t>
-  </si>
-  <si>
-    <t>Algorytm L4 (capacity, bez obniżania puli)</t>
-  </si>
-  <si>
-    <t>Jako system chcę traktować L4 dla UoP jako wpływające na capacity, lecz nie na pulę urlopu, aby poprawnie odwzorować chorobowe.</t>
+    <t xml:space="preserve">FR-B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algorytm L4 (capacity, bez obniżania puli)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako system chcę traktować L4 dla UoP jako wpływające na capacity, lecz nie na pulę urlopu, aby poprawnie odwzorować chorobowe.</t>
   </si>
   <si>
     <t xml:space="preserve">• Wpis L4 zmniejsza dostępność w capacity
 • Wpis L4 nie pomniejsza puli urlopu UoP</t>
   </si>
   <si>
-    <t>FR-B5</t>
-  </si>
-  <si>
-    <t>US-B6</t>
-  </si>
-  <si>
-    <t>Wymiar B2B/OUT ustalany per okres</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę ustawić wymiar B2B/OUT dla danego okresu, aby odwzorować różny wymiar (np. odbiory za święta).</t>
+    <t xml:space="preserve">FR-B5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wymiar B2B/OUT ustalany per okres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę ustawić wymiar B2B/OUT dla danego okresu, aby odwzorować różny wymiar (np. odbiory za święta).</t>
   </si>
   <si>
     <t xml:space="preserve">• Wymiar ustawiany w panelu admina
 • Możliwa korekta indywidualna</t>
   </si>
   <si>
-    <t>FR-B6</t>
-  </si>
-  <si>
-    <t>US-B7</t>
-  </si>
-  <si>
-    <t>Przełom okresu — rolowanie/wygaszanie urlopu</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę, żeby niewykorzystane dni przeszły na kolejny okres rozliczeniowy, aby nie tracić urlopu na przełomie roku.</t>
+    <t xml:space="preserve">FR-B6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przełom okresu — rolowanie/wygaszanie urlopu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę, żeby niewykorzystane dni przeszły na kolejny okres rozliczeniowy, aby nie tracić urlopu na przełomie roku.</t>
   </si>
   <si>
     <t xml:space="preserve">• Niewykorzystane dni przechodzą do kolejnego okresu jako zaległe, bez terminu wygaśnięcia
@@ -389,76 +395,76 @@
 • Licznik na pulpicie i raport wykorzystania pokazują tę samą liczbę dni zaległych</t>
   </si>
   <si>
-    <t>FR-B7</t>
-  </si>
-  <si>
-    <t>Zrealizowane — reguła rozstrzygnięta (urlop nie przepada); kryteria akceptacji poprawione 10.08.2026</t>
-  </si>
-  <si>
-    <t>US-B8</t>
-  </si>
-  <si>
-    <t>Zmiana formy zatrudnienia w trakcie roku</t>
-  </si>
-  <si>
-    <t>Jako system chcę zastosować właściwe reguły po zmianie formy (np. B2B→UoP), aby zachować poprawność wyliczeń i historię.</t>
+    <t xml:space="preserve">FR-B7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — reguła rozstrzygnięta (urlop nie przepada); kryteria akceptacji poprawione 10.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zmiana formy zatrudnienia w trakcie roku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako system chcę zastosować właściwe reguły po zmianie formy (np. B2B→UoP), aby zachować poprawność wyliczeń i historię.</t>
   </si>
   <si>
     <t xml:space="preserve">• Po dacie zmiany obowiązuje właściwy okres
 • Historia sprzed zmiany zachowana</t>
   </si>
   <si>
-    <t>FR-B8</t>
-  </si>
-  <si>
-    <t>US-B9</t>
-  </si>
-  <si>
-    <t>Proporcjonalne naliczanie puli (proration)</t>
-  </si>
-  <si>
-    <t>Jako system chcę naliczać pulę proporcjonalnie przy wejściu/odejściu w trakcie okresu, aby sprawiedliwie liczyć limit dla nowych i odchodzących.</t>
+    <t xml:space="preserve">FR-B8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proporcjonalne naliczanie puli (proration)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako system chcę naliczać pulę proporcjonalnie przy wejściu/odejściu w trakcie okresu, aby sprawiedliwie liczyć limit dla nowych i odchodzących.</t>
   </si>
   <si>
     <t xml:space="preserve">• Pula proporcjonalna do okresu zatrudnienia
 • Nieobecności po dacie odejścia sygnalizowane</t>
   </si>
   <si>
-    <t>FR-B9</t>
-  </si>
-  <si>
-    <t>US-B10</t>
-  </si>
-  <si>
-    <t>Konwersja zaplanowanej nieobecności na L4</t>
-  </si>
-  <si>
-    <t>Jako osoba z uprawnieniem rozszerzonym chcę zamienić zaplanowany urlop na L4 po fakcie, aby oddać dzień do puli, gdy pracownik zachorował.</t>
+    <t xml:space="preserve">FR-B9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konwersja zaplanowanej nieobecności na L4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako osoba z uprawnieniem rozszerzonym chcę zamienić zaplanowany urlop na L4 po fakcie, aby oddać dzień do puli, gdy pracownik zachorował.</t>
   </si>
   <si>
     <t xml:space="preserve">• Dzień zamieniony na L4 wraca do puli UoP
 • Zmiana odnotowana w historii</t>
   </si>
   <si>
-    <t>FR-B10</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>Kalendarz i widoki zespołu</t>
-  </si>
-  <si>
-    <t>Wspólny, jednolity widok nieobecności w obrębie Tribe.</t>
-  </si>
-  <si>
-    <t>US-C1</t>
-  </si>
-  <si>
-    <t>Kalendarz zespołu (tydzień/miesiąc)</t>
-  </si>
-  <si>
-    <t>Jako lider / pracownik chcę widzieć nieobecności zespołu w kalendarzu, aby planować pracę z wyprzedzeniem.</t>
+    <t xml:space="preserve">FR-B10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalendarz i widoki zespołu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wspólny, jednolity widok nieobecności w obrębie Tribe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalendarz zespołu (tydzień/miesiąc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider / pracownik chcę widzieć nieobecności zespołu w kalendarzu, aby planować pracę z wyprzedzeniem.</t>
   </si>
   <si>
     <t xml:space="preserve">• Widok tygodniowy i miesięczny
@@ -466,251 +472,251 @@
 • Możliwość filtrowania</t>
   </si>
   <si>
-    <t>FR-C1</t>
-  </si>
-  <si>
-    <t>US-C2</t>
-  </si>
-  <si>
-    <t>Filtr „kto dziś / w tym tygodniu nieobecny”</t>
-  </si>
-  <si>
-    <t>Jako lider chcę szybko zawęzić widok do nieobecnych, aby ocenić bieżącą dostępność zespołu.</t>
+    <t xml:space="preserve">FR-C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtr „kto dziś / w tym tygodniu nieobecny”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider chcę szybko zawęzić widok do nieobecnych, aby ocenić bieżącą dostępność zespołu.</t>
   </si>
   <si>
     <t xml:space="preserve">• Filtr zawęża do wybranego horyzontu
 • Wynik aktualny na bieżący dzień/tydzień</t>
   </si>
   <si>
-    <t>FR-C2</t>
-  </si>
-  <si>
-    <t>US-C3</t>
-  </si>
-  <si>
-    <t>Jednolita prezentacja nieobecności</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę widzieć wszystkie nieobecności jednolicie (bez kolorów per typ), aby chronić prywatność i uprościć odbiór.</t>
+    <t xml:space="preserve">FR-C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jednolita prezentacja nieobecności</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę widzieć wszystkie nieobecności jednolicie (bez kolorów per typ), aby chronić prywatność i uprościć odbiór.</t>
   </si>
   <si>
     <t xml:space="preserve">• Brak kolorów per typ
 • L4 wyświetlane jak zwykła nieobecność (bez etykiety „chorobowe”)</t>
   </si>
   <si>
-    <t>FR-C3</t>
-  </si>
-  <si>
-    <t>US-C4</t>
-  </si>
-  <si>
-    <t>Heatmapa pokrycia zespołu</t>
-  </si>
-  <si>
-    <t>Jako lider chcę zobaczyć natężenie nieobecności w czasie, aby wykryć okresy ryzyka pokrycia.</t>
-  </si>
-  <si>
-    <t>• Okresy o wysokim odsetku nieobecności wyróżnione</t>
-  </si>
-  <si>
-    <t>FR-C4</t>
-  </si>
-  <si>
-    <t>US-C5</t>
-  </si>
-  <si>
-    <t>Pulpit startowy</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę mieć po zalogowaniu mój balans, kto nieobecny i przypomnienia, aby od razu widzieć najważniejsze informacje.</t>
+    <t xml:space="preserve">FR-C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heatmapa pokrycia zespołu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider chcę zobaczyć natężenie nieobecności w czasie, aby wykryć okresy ryzyka pokrycia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Okresy o wysokim odsetku nieobecności wyróżnione</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulpit startowy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę mieć po zalogowaniu mój balans, kto nieobecny i przypomnienia, aby od razu widzieć najważniejsze informacje.</t>
   </si>
   <si>
     <t xml:space="preserve">• Domyślny ekran prezentuje balans, listę nieobecnych i przypomnienia
 • Brak dodatkowej nawigacji do kluczowych danych</t>
   </si>
   <si>
-    <t>FR-C5</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>Planowanie capacity i sprinty</t>
-  </si>
-  <si>
-    <t>Wsparcie planowania sprintów i ostrzeganie o ryzyku pokrycia ról.</t>
-  </si>
-  <si>
-    <t>US-D1</t>
-  </si>
-  <si>
-    <t>Widok sprintowy nieobecności</t>
-  </si>
-  <si>
-    <t>Jako Product Owner / Agile PM chcę widzieć nieobecności w podziale na sprinty, aby planować zakres sprintu realistycznie.</t>
+    <t xml:space="preserve">FR-C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planowanie capacity i sprinty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wsparcie planowania sprintów i ostrzeganie o ryzyku pokrycia ról.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widok sprintowy nieobecności</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako Product Owner / Agile PM chcę widzieć nieobecności w podziale na sprinty, aby planować zakres sprintu realistycznie.</t>
   </si>
   <si>
     <t xml:space="preserve">• Wybór sprintu
 • Podgląd nieobecności i capacity squadu w sprincie</t>
   </si>
   <si>
-    <t>FR-D1</t>
-  </si>
-  <si>
-    <t>US-D2</t>
-  </si>
-  <si>
-    <t>Wyliczenie capacity squadu per sprint</t>
-  </si>
-  <si>
-    <t>Jako Product Owner / Agile PM chcę mieć policzone capacity squadu na sprint, aby oszacować realny potencjał wykonawczy.</t>
+    <t xml:space="preserve">FR-D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyliczenie capacity squadu per sprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako Product Owner / Agile PM chcę mieć policzone capacity squadu na sprint, aby oszacować realny potencjał wykonawczy.</t>
   </si>
   <si>
     <t xml:space="preserve">• Capacity pomniejszone o nieobecności i niepełne dni
 • Przeliczane automatycznie na bazie wpisów i kalendarza sprintów</t>
   </si>
   <si>
-    <t>FR-D2</t>
-  </si>
-  <si>
-    <t>US-D3</t>
-  </si>
-  <si>
-    <t>Alert kolizji kluczowych ról</t>
-  </si>
-  <si>
-    <t>Jako Product Owner / lider chcę otrzymać ostrzeżenie, gdy kluczowe role są nieobecne jednocześnie, aby ograniczyć ryzyko ciągłości.</t>
+    <t xml:space="preserve">FR-D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alert kolizji kluczowych ról</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako Product Owner / lider chcę otrzymać ostrzeżenie, gdy kluczowe role są nieobecne jednocześnie, aby ograniczyć ryzyko ciągłości.</t>
   </si>
   <si>
     <t xml:space="preserve">• Role kluczowe oznacza administrator
 • System sygnalizuje nakładające się nieobecności kluczowych ról</t>
   </si>
   <si>
-    <t>FR-D3</t>
-  </si>
-  <si>
-    <t>US-D4</t>
-  </si>
-  <si>
-    <t>Import harmonogramu sprintów</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę zaimportować harmonogram sprintów z pliku .xlsx, aby zasilić widoki i wyliczenia sprintowe.</t>
+    <t xml:space="preserve">FR-D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import harmonogramu sprintów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę zaimportować harmonogram sprintów z pliku .xlsx, aby zasilić widoki i wyliczenia sprintowe.</t>
   </si>
   <si>
     <t xml:space="preserve">• Import .xlsx ram sprintów
 • Ramy używane w widokach i capacity</t>
   </si>
   <si>
-    <t>FR-D4</t>
-  </si>
-  <si>
-    <t>Zrealizowane — układ kolumn pliku konfigurowalny do czasu decyzji zamawiającego</t>
-  </si>
-  <si>
-    <t>E5</t>
-  </si>
-  <si>
-    <t>Powiadomienia</t>
-  </si>
-  <si>
-    <t>Informowanie liderów i pracowników o istotnych zdarzeniach.</t>
-  </si>
-  <si>
-    <t>US-E1</t>
-  </si>
-  <si>
-    <t>Powiadomienie lidera o nieobecności B2B/OUT</t>
-  </si>
-  <si>
-    <t>Jako lider chcę dostać e-mail o planowanej nieobecności B2B/OUT, aby być informowanym bez formalnej akceptacji.</t>
+    <t xml:space="preserve">FR-D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — układ kolumn pliku konfigurowalny do czasu decyzji zamawiającego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powiadomienia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informowanie liderów i pracowników o istotnych zdarzeniach.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powiadomienie lidera o nieobecności B2B/OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider chcę dostać e-mail o planowanej nieobecności B2B/OUT, aby być informowanym bez formalnej akceptacji.</t>
   </si>
   <si>
     <t xml:space="preserve">• E-mail do lidera &lt; 5 min od zapisania wpisu B2B/OUT
 • Charakter informacyjny (bez zatwierdzania)</t>
   </si>
   <si>
-    <t>FR-E1</t>
-  </si>
-  <si>
-    <t>US-E2</t>
-  </si>
-  <si>
-    <t>Wpis bez formalnej akceptacji</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę mieć wpis obowiązujący od zapisania, aby uniknąć zbędnego obiegu akceptacji.</t>
-  </si>
-  <si>
-    <t>• Wpis widoczny i uwzględniony w wyliczeniach bez zatwierdzania</t>
-  </si>
-  <si>
-    <t>FR-E2</t>
-  </si>
-  <si>
-    <t>US-E3</t>
-  </si>
-  <si>
-    <t>Przypomnienia o zaległym/niewybranym urlopie</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę otrzymywać przypomnienia o zaległym urlopie, aby wykorzystać dni zanim przepadną.</t>
+    <t xml:space="preserve">FR-E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wpis bez formalnej akceptacji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę mieć wpis obowiązujący od zapisania, aby uniknąć zbędnego obiegu akceptacji.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Wpis widoczny i uwzględniony w wyliczeniach bez zatwierdzania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przypomnienia o zaległym/niewybranym urlopie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę otrzymywać przypomnienia o zaległym urlopie, aby wykorzystać dni zanim przepadną.</t>
   </si>
   <si>
     <t xml:space="preserve">• Przypomnienie wg reguły administratora
 • Opcjonalna kopia do lidera</t>
   </si>
   <si>
-    <t>FR-E3</t>
-  </si>
-  <si>
-    <t>US-E4</t>
-  </si>
-  <si>
-    <t>Kanał powiadomień e-mail</t>
-  </si>
-  <si>
-    <t>Jako system chcę wysyłać powiadomienia e-mailem, aby dostarczać informacje w MVP bez dodatkowych kanałów.</t>
-  </si>
-  <si>
-    <t>• Powiadomienia dostarczane e-mailem &lt; 5 min od zdarzenia</t>
-  </si>
-  <si>
-    <t>FR-E4</t>
-  </si>
-  <si>
-    <t>E6</t>
-  </si>
-  <si>
-    <t>Raporty i eksport</t>
-  </si>
-  <si>
-    <t>Raportowanie z drążeniem hierarchii i eksportem do Excela.</t>
-  </si>
-  <si>
-    <t>US-F1</t>
-  </si>
-  <si>
-    <t>Eksport danych i raportów do Excela</t>
-  </si>
-  <si>
-    <t>Jako lider / PMO chcę wyeksportować dane do .xlsx, aby pracować dalej w arkuszu i archiwizować.</t>
+    <t xml:space="preserve">FR-E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanał powiadomień e-mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako system chcę wysyłać powiadomienia e-mailem, aby dostarczać informacje w MVP bez dodatkowych kanałów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Powiadomienia dostarczane e-mailem &lt; 5 min od zdarzenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raporty i eksport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raportowanie z drążeniem hierarchii i eksportem do Excela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eksport danych i raportów do Excela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider / PMO chcę wyeksportować dane do .xlsx, aby pracować dalej w arkuszu i archiwizować.</t>
   </si>
   <si>
     <t xml:space="preserve">• Eksport zawiera wymagane pola
 • Plik otwiera się poprawnie w Excelu</t>
   </si>
   <si>
-    <t>FR-F1</t>
-  </si>
-  <si>
-    <t>US-F2</t>
-  </si>
-  <si>
-    <t>Raporty predefiniowane per rola</t>
-  </si>
-  <si>
-    <t>Jako lider / dyrektor chcę generować gotowe raporty w swoim zakresie, aby szybko ocenić wykorzystanie i nieobecności.</t>
+    <t xml:space="preserve">FR-F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raporty predefiniowane per rola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider / dyrektor chcę generować gotowe raporty w swoim zakresie, aby szybko ocenić wykorzystanie i nieobecności.</t>
   </si>
   <si>
     <t xml:space="preserve">• Raport per pracownik, squad/sprint, Tribe, departament
@@ -718,136 +724,136 @@
 • Informacja o formie współpracy</t>
   </si>
   <si>
-    <t>FR-F2</t>
-  </si>
-  <si>
-    <t>US-F3</t>
-  </si>
-  <si>
-    <t>Agregacja i drążenie hierarchii</t>
-  </si>
-  <si>
-    <t>Jako dyrektor / lider chcę drążyć dane pion › departament › Tribe › squad › osoba, aby analizować na dowolnym poziomie.</t>
+    <t xml:space="preserve">FR-F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregacja i drążenie hierarchii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako dyrektor / lider chcę drążyć dane pion › departament › Tribe › squad › osoba, aby analizować na dowolnym poziomie.</t>
   </si>
   <si>
     <t xml:space="preserve">• Przechodzenie między poziomami
 • Dane sumują się automatycznie w górę</t>
   </si>
   <si>
-    <t>FR-F3</t>
-  </si>
-  <si>
-    <t>US-F4</t>
-  </si>
-  <si>
-    <t>Eksport do kalendarza Outlook/iCal</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę wyeksportować nieobecności do kalendarza, aby widzieć je w Outlooku.</t>
+    <t xml:space="preserve">FR-F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eksport do kalendarza Outlook/iCal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę wyeksportować nieobecności do kalendarza, aby widzieć je w Outlooku.</t>
   </si>
   <si>
     <t xml:space="preserve">• Nieobecności jako wydarzenia kalendarzowe
 • Funkcja po MVP</t>
   </si>
   <si>
-    <t>FR-F4</t>
-  </si>
-  <si>
-    <t>US-F5</t>
-  </si>
-  <si>
-    <t>Raport „kto zalega”</t>
-  </si>
-  <si>
-    <t>Jako lider / dyrektor chcę zobaczyć osoby zalegające z wybraniem urlopu, aby reagować na ryzyko kumulacji.</t>
-  </si>
-  <si>
-    <t>• Raport wskazuje osoby z zaległym/niewybranym urlopem</t>
-  </si>
-  <si>
-    <t>FR-F5</t>
-  </si>
-  <si>
-    <t>US-F6</t>
-  </si>
-  <si>
-    <t>Stabilny schemat eksportu dla PMO/płac</t>
-  </si>
-  <si>
-    <t>Jako PMO chcę mieć udokumentowany, stabilny format eksportu, aby umożliwić późniejszą integrację bez przebudowy.</t>
+    <t xml:space="preserve">FR-F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raport „kto zalega”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako lider / dyrektor chcę zobaczyć osoby zalegające z wybraniem urlopu, aby reagować na ryzyko kumulacji.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Raport wskazuje osoby z zaległym/niewybranym urlopem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stabilny schemat eksportu dla PMO/płac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako PMO chcę mieć udokumentowany, stabilny format eksportu, aby umożliwić późniejszą integrację bez przebudowy.</t>
   </si>
   <si>
     <t xml:space="preserve">• Udokumentowany schemat pól
 • Zmiany wersjonowane</t>
   </si>
   <si>
-    <t>FR-F6</t>
-  </si>
-  <si>
-    <t>E7</t>
-  </si>
-  <si>
-    <t>Administracja</t>
-  </si>
-  <si>
-    <t>Konfiguracja typów, puli, świąt, struktury i sprintów.</t>
-  </si>
-  <si>
-    <t>US-G1</t>
-  </si>
-  <si>
-    <t>Zarządzanie typami nieobecności</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę dodawać/edytować typy i ich reguły w trybie live, aby dostosować słownik typów bez zmian w kodzie.</t>
+    <t xml:space="preserve">FR-F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administracja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konfiguracja typów, puli, świąt, struktury i sprintów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarządzanie typami nieobecności</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę dodawać/edytować typy i ich reguły w trybie live, aby dostosować słownik typów bez zmian w kodzie.</t>
   </si>
   <si>
     <t xml:space="preserve">• Edycja typów i reguł (limity, wpływ na algorytm, kategoria szczególna)
 • Zmiany widoczne natychmiast</t>
   </si>
   <si>
-    <t>FR-G1</t>
-  </si>
-  <si>
-    <t>US-G2</t>
-  </si>
-  <si>
-    <t>Zarządzanie pulą urlopu</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę ustawiać pulę globalną i korekty, aby utrzymywać limity urlopowe.</t>
+    <t xml:space="preserve">FR-G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarządzanie pulą urlopu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę ustawiać pulę globalną i korekty, aby utrzymywać limity urlopowe.</t>
   </si>
   <si>
     <t xml:space="preserve">• Wartość globalna i korekta indywidualna
 • Zmiany odzwierciedlone w licznikach</t>
   </si>
   <si>
-    <t>FR-G2</t>
-  </si>
-  <si>
-    <t>US-G3</t>
-  </si>
-  <si>
-    <t>Tabela świąt i dni wolnych</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę zarządzać świętami i dniami wolnymi (w tym odbiorami), aby poprawnie pomijać dni przy liczeniu.</t>
+    <t xml:space="preserve">FR-G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabela świąt i dni wolnych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę zarządzać świętami i dniami wolnymi (w tym odbiorami), aby poprawnie pomijać dni przy liczeniu.</t>
   </si>
   <si>
     <t xml:space="preserve">• Dodawanie/edycja dni
 • Dni pomijane przy liczeniu nieobecności i capacity</t>
   </si>
   <si>
-    <t>FR-G3</t>
-  </si>
-  <si>
-    <t>US-G4</t>
-  </si>
-  <si>
-    <t>Zarządzanie strukturą organizacyjną</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę budować hierarchię jednostek i przypisywać osoby do wielu jednostek, aby odwzorować strukturę Tribe/squad.</t>
+    <t xml:space="preserve">FR-G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarządzanie strukturą organizacyjną</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę budować hierarchię jednostek i przypisywać osoby do wielu jednostek, aby odwzorować strukturę Tribe/squad.</t>
   </si>
   <si>
     <t xml:space="preserve">• Hierarchia pion›departament›Tribe›chapter/squad
@@ -855,16 +861,16 @@
 • Dane osoby agregują się we wszystkich jednostkach</t>
   </si>
   <si>
-    <t>FR-G4</t>
-  </si>
-  <si>
-    <t>US-G5</t>
-  </si>
-  <si>
-    <t>Zarządzanie pracownikami i import .xlsx</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę zaimportować pracowników z .xlsx i ręcznie budować drzewo, aby zasilić aplikację bez integracji z AD.</t>
+    <t xml:space="preserve">FR-G4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarządzanie pracownikami i import .xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę zaimportować pracowników z .xlsx i ręcznie budować drzewo, aby zasilić aplikację bez integracji z AD.</t>
   </si>
   <si>
     <t xml:space="preserve">• Import .xlsx listy pracowników
@@ -872,73 +878,73 @@
 • Utrzymanie formy zatrudnienia każdej osoby</t>
   </si>
   <si>
-    <t>FR-G5</t>
-  </si>
-  <si>
-    <t>US-G6</t>
-  </si>
-  <si>
-    <t>Zarządzanie definicjami sprintów</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę definiować i aktualizować ramy sprintów, aby utrzymywać aktualny harmonogram.</t>
+    <t xml:space="preserve">FR-G5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarządzanie definicjami sprintów</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę definiować i aktualizować ramy sprintów, aby utrzymywać aktualny harmonogram.</t>
   </si>
   <si>
     <t xml:space="preserve">• Tworzenie/aktualizacja ram sprintów
 • Ramy używane w widokach sprintowych</t>
   </si>
   <si>
-    <t>FR-G6</t>
-  </si>
-  <si>
-    <t>US-G7</t>
-  </si>
-  <si>
-    <t>Wiele kalendarzy świąt</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę przypisywać kalendarz świąt do osoby/lokalizacji, aby obsłużyć B2B/OUT z innych lokalizacji.</t>
+    <t xml:space="preserve">FR-G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiele kalendarzy świąt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę przypisywać kalendarz świąt do osoby/lokalizacji, aby obsłużyć B2B/OUT z innych lokalizacji.</t>
   </si>
   <si>
     <t xml:space="preserve">• Wpisy uwzględniają kalendarz właściwy dla osoby
 • Domyślnie jeden kalendarz organizacji</t>
   </si>
   <si>
-    <t>FR-G7</t>
-  </si>
-  <si>
-    <t>E8</t>
-  </si>
-  <si>
-    <t>Uprawnienia, role i logowanie</t>
-  </si>
-  <si>
-    <t>Kontrola dostępu, delegacja uprawnień i uwierzytelnianie.</t>
-  </si>
-  <si>
-    <t>US-H1</t>
-  </si>
-  <si>
-    <t>Widoczność w obrębie Tribe + filtry squad</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę widzieć nieobecności osób w swoim Tribe z filtrem squadu, aby mieć wspólny obraz zespołu.</t>
+    <t xml:space="preserve">FR-G7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uprawnienia, role i logowanie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrola dostępu, delegacja uprawnień i uwierzytelnianie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widoczność w obrębie Tribe + filtry squad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę widzieć nieobecności osób w swoim Tribe z filtrem squadu, aby mieć wspólny obraz zespołu.</t>
   </si>
   <si>
     <t xml:space="preserve">• Widoczność w obrębie Tribe
 • Filtry zawężają do squadu</t>
   </si>
   <si>
-    <t>FR-H1</t>
-  </si>
-  <si>
-    <t>US-H2</t>
-  </si>
-  <si>
-    <t>Widoki wg roli (podstawowy RBAC)</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę ograniczyć zakres danych i funkcji do roli, aby chronić dane i uprościć interfejs.</t>
+    <t xml:space="preserve">FR-H1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-H2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widoki wg roli (podstawowy RBAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę ograniczyć zakres danych i funkcji do roli, aby chronić dane i uprościć interfejs.</t>
   </si>
   <si>
     <t xml:space="preserve">• Każda rola ma adekwatny zakres
@@ -946,242 +952,245 @@
 • Pełny RBAC etapowo</t>
   </si>
   <si>
-    <t>FR-H2</t>
-  </si>
-  <si>
-    <t>US-H3</t>
-  </si>
-  <si>
-    <t>Brak wyróżnienia chorobowego</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę nie widzieć etykiety „chorobowe” w żadnym widoku, aby chronić dane wrażliwe współpracowników.</t>
-  </si>
-  <si>
-    <t>• Etykieta „chorobowe” nie pojawia się w UI ani w eksportach widocznych dla zespołu</t>
-  </si>
-  <si>
-    <t>FR-H3</t>
-  </si>
-  <si>
-    <t>US-H4</t>
-  </si>
-  <si>
-    <t>Zarządzanie rolami i delegacja uprawnień</t>
-  </si>
-  <si>
-    <t>Jako administrator / menedżer chcę nadawać uprawnienia rozszerzone wskazanym osobom, aby umożliwić np. dodawanie L4 w imieniu innych.</t>
+    <t xml:space="preserve">FR-H2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-H3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brak wyróżnienia chorobowego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę nie widzieć etykiety „chorobowe” w żadnym widoku, aby chronić dane wrażliwe współpracowników.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Etykieta „chorobowe” nie pojawia się w UI ani w eksportach widocznych dla zespołu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-H3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-H4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zarządzanie rolami i delegacja uprawnień</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator / menedżer chcę nadawać uprawnienia rozszerzone wskazanym osobom, aby umożliwić np. dodawanie L4 w imieniu innych.</t>
   </si>
   <si>
     <t xml:space="preserve">• Nadawanie/odbieranie uprawnień
 • Zakres uprawnień widoczny i audytowalny</t>
   </si>
   <si>
-    <t>FR-H4</t>
-  </si>
-  <si>
-    <t>US-H5</t>
-  </si>
-  <si>
-    <t>Logowanie w aplikacji (docelowo SSO)</t>
-  </si>
-  <si>
-    <t>Jako użytkownik chcę logować się kontem w aplikacji, aby bezpiecznie korzystać z systemu w MVP.</t>
+    <t xml:space="preserve">FR-H4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-H5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logowanie w aplikacji (docelowo SSO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako użytkownik chcę logować się kontem w aplikacji, aby bezpiecznie korzystać z systemu w MVP.</t>
   </si>
   <si>
     <t xml:space="preserve">• Logowanie kontem w aplikacji
 • Architektura przygotowana na późniejsze SSO przez AD</t>
   </si>
   <si>
-    <t>FR-H5</t>
-  </si>
-  <si>
-    <t>Zrealizowane — logowanie kontem w aplikacji; SSO/OIDC poza zakresem historyjki (przygotowany szew AuthProvider)</t>
-  </si>
-  <si>
-    <t>E9</t>
-  </si>
-  <si>
-    <t>Audyt i historia</t>
-  </si>
-  <si>
-    <t>Śledzenie zmian i wgląd we własną historię wpisów.</t>
-  </si>
-  <si>
-    <t>US-I1</t>
-  </si>
-  <si>
-    <t>Historia zmian wpisu</t>
-  </si>
-  <si>
-    <t>Jako administrator / lider chcę mieć dziennik zmian (kto, kiedy, co), aby zapewnić rozliczalność i audyt.</t>
+    <t xml:space="preserve">FR-H5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — logowanie kontem w aplikacji; SSO/OIDC poza zakresem historyjki (przygotowany szew AuthProvider)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audyt i historia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Śledzenie zmian i wgląd we własną historię wpisów.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-I1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historia zmian wpisu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator / lider chcę mieć dziennik zmian (kto, kiedy, co), aby zapewnić rozliczalność i audyt.</t>
   </si>
   <si>
     <t xml:space="preserve">• Każda operacja zapisana z użytkownikiem i znacznikiem czasu
 • Dziennik niemodyfikowalny</t>
   </si>
   <si>
-    <t>FR-I1</t>
-  </si>
-  <si>
-    <t>US-I2</t>
-  </si>
-  <si>
-    <t>Podgląd własnej historii i wycofanie wpisu</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę widzieć swoją historię i wycofać własny wpis, aby kontrolować własne dane.</t>
+    <t xml:space="preserve">FR-I1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-I2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podgląd własnej historii i wycofanie wpisu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę widzieć swoją historię i wycofać własny wpis, aby kontrolować własne dane.</t>
   </si>
   <si>
     <t xml:space="preserve">• Lista z sortowaniem i filtrowaniem
 • Wycofanie aktualizuje balans</t>
   </si>
   <si>
-    <t>FR-I2</t>
-  </si>
-  <si>
-    <t>E10</t>
-  </si>
-  <si>
-    <t>Bezpieczeństwo i zgodność (RODO)</t>
-  </si>
-  <si>
-    <t>Ochrona danych o zdrowiu (L4) i zgodność z RODO.</t>
-  </si>
-  <si>
-    <t>US-J1</t>
-  </si>
-  <si>
-    <t>Ochrona znacznika L4 (dane o zdrowiu)</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę ograniczyć dostęp do informacji „to jest L4” do ról uprawnionych, aby spełnić wymóg art. 9 RODO.</t>
+    <t xml:space="preserve">FR-I2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezpieczeństwo i zgodność (RODO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ochrona danych o zdrowiu (L4) i zgodność z RODO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-J1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ochrona znacznika L4 (dane o zdrowiu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę ograniczyć dostęp do informacji „to jest L4” do ról uprawnionych, aby spełnić wymóg art. 9 RODO.</t>
   </si>
   <si>
     <t xml:space="preserve">• Tylko uprawnione role widzą znacznik L4
 • Próba odczytu przez nieuprawnioną rolę blokowana i logowana</t>
   </si>
   <si>
-    <t>FR-J1</t>
-  </si>
-  <si>
-    <t>US-J2</t>
-  </si>
-  <si>
-    <t>Retencja i usuwanie danych</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę zdefiniować okres przechowywania i usuwać dane byłych pracowników, aby realizować prawo do bycia zapomnianym.</t>
+    <t xml:space="preserve">FR-J1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — audyt odczytu znacznika L4 rozszerzony na eksport płacowy (przegląd kodu 10.08.2026); wcześniej audytowany był wyłącznie odczyt przez /absences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retencja i usuwanie danych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę zdefiniować okres przechowywania i usuwać dane byłych pracowników, aby realizować prawo do bycia zapomnianym.</t>
   </si>
   <si>
     <t xml:space="preserve">• Zdefiniowany okres retencji
 • Po jego upływie dane anonimizowane lub usuwane</t>
   </si>
   <si>
-    <t>FR-J2</t>
-  </si>
-  <si>
-    <t>US-J3</t>
-  </si>
-  <si>
-    <t>Minimalizacja, podstawa prawna, rejestr czynności</t>
-  </si>
-  <si>
-    <t>Jako administrator / IOD chcę przetwarzać tylko niezbędne dane i prowadzić rejestr, aby zachować zgodność z RODO.</t>
+    <t xml:space="preserve">FR-J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-J3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimalizacja, podstawa prawna, rejestr czynności</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator / IOD chcę przetwarzać tylko niezbędne dane i prowadzić rejestr, aby zachować zgodność z RODO.</t>
   </si>
   <si>
     <t xml:space="preserve">• Zakres pól ograniczony do niezbędnych
 • Dostępny rejestr czynności przetwarzania i podstawa prawna</t>
   </si>
   <si>
-    <t>FR-J3</t>
-  </si>
-  <si>
-    <t>US-J4</t>
-  </si>
-  <si>
-    <t>Bezpieczne eksporty (bez znacznika L4)</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę zapewnić, że eksporty nie ujawniają L4 nieuprawnionym, aby nie wynosić danych szczególnych.</t>
-  </si>
-  <si>
-    <t>• Eksport dla ról nieuprawnionych nie zawiera kategorii szczególnej</t>
-  </si>
-  <si>
-    <t>FR-J4</t>
-  </si>
-  <si>
-    <t>E11</t>
-  </si>
-  <si>
-    <t>Platforma i wymagania niefunkcjonalne</t>
-  </si>
-  <si>
-    <t>Wydajność, bezpieczeństwo, backup, dostępność i analityka.</t>
-  </si>
-  <si>
-    <t>US-N1</t>
-  </si>
-  <si>
-    <t>Wydajność pulpitu i licznika</t>
-  </si>
-  <si>
-    <t>Jako użytkownik chcę mieć szybki pulpit i licznik, aby komfortowo korzystać przy 300 użytkownikach.</t>
+    <t xml:space="preserve">FR-J3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-J4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezpieczne eksporty (bez znacznika L4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę zapewnić, że eksporty nie ujawniają L4 nieuprawnionym, aby nie wynosić danych szczególnych.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Eksport dla ról nieuprawnionych nie zawiera kategorii szczególnej</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-J4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platforma i wymagania niefunkcjonalne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wydajność, bezpieczeństwo, backup, dostępność i analityka.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wydajność pulpitu i licznika</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako użytkownik chcę mieć szybki pulpit i licznik, aby komfortowo korzystać przy 300 użytkownikach.</t>
   </si>
   <si>
     <t xml:space="preserve">• Pulpit/kalendarz ładują się &lt; 2 s przy 300 użytkownikach
 • Licznik balansu odświeża się &lt; 1 s</t>
   </si>
   <si>
-    <t>NFR-1</t>
-  </si>
-  <si>
-    <t>Zrealizowane — zweryfikowane testem obciążeniowym 300 użytkowników (10.08.2026)</t>
-  </si>
-  <si>
-    <t>US-N2</t>
-  </si>
-  <si>
-    <t>Monitoring dostępności (SLA)</t>
-  </si>
-  <si>
-    <t>Jako zespół utrzymania chcę monitorować dostępność i otrzymywać alerty, aby reagować na incydenty.</t>
+    <t xml:space="preserve">NFR-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — zweryfikowane testem obciążeniowym 300 użytkowników (10.08.2026); ekran capacity sprintu pobiera siatkę jednym żądaniem zamiast jednego na squad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring dostępności (SLA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako zespół utrzymania chcę monitorować dostępność i otrzymywać alerty, aby reagować na incydenty.</t>
   </si>
   <si>
     <t xml:space="preserve">• Monitoring dostępności w godzinach pracy
 • Alerty przy przekroczeniu progów</t>
   </si>
   <si>
-    <t>NFR-2</t>
-  </si>
-  <si>
-    <t>Zrealizowane częściowo — sonda /api/health w aplikacji; progi i alerty po stronie monitoringu organizacji</t>
-  </si>
-  <si>
-    <t>US-N3</t>
-  </si>
-  <si>
-    <t>Skalowalność architektury</t>
-  </si>
-  <si>
-    <t>Jako architekt chcę zapewnić zapas na wzrost organizacji, aby uniknąć przebudowy w przyszłości.</t>
+    <t xml:space="preserve">NFR-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane częściowo — sonda /api/health w aplikacji, healthcheck bazy i API w compose produkcyjnym; progi i alerty po stronie monitoringu organizacji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skalowalność architektury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako architekt chcę zapewnić zapas na wzrost organizacji, aby uniknąć przebudowy w przyszłości.</t>
   </si>
   <si>
     <t xml:space="preserve">• Obsługa min. 300 użytkowników z zapasem
 • Brak twardych limitów blokujących wzrost</t>
   </si>
   <si>
-    <t>NFR-3</t>
-  </si>
-  <si>
-    <t>US-N4</t>
-  </si>
-  <si>
-    <t>Backup i odtwarzanie</t>
-  </si>
-  <si>
-    <t>Jako zespół utrzymania chcę mieć codzienny backup i zdefiniowane RPO/RTO, aby zabezpieczyć dane przed utratą.</t>
+    <t xml:space="preserve">NFR-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup i odtwarzanie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako zespół utrzymania chcę mieć codzienny backup i zdefiniowane RPO/RTO, aby zabezpieczyć dane przed utratą.</t>
   </si>
   <si>
     <t xml:space="preserve">• Codzienny backup bazy
@@ -1189,16 +1198,19 @@
 • Okresowy test odtwarzania</t>
   </si>
   <si>
-    <t>NFR-4</t>
-  </si>
-  <si>
-    <t>US-N5</t>
-  </si>
-  <si>
-    <t>Bezpieczeństwo danych</t>
-  </si>
-  <si>
-    <t>Jako zespół bezpieczeństwa chcę szyfrować dane i kontrolować dostęp, aby chronić dane osobowe i wrażliwe.</t>
+    <t xml:space="preserve">NFR-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — test odtworzenia zautomatyzowany (scripts/restore-test.sh, do uruchamiania kwartalnie); przebieg 10.08.2026 na dumpie bazy demo: Employee=23, Absence=49, wynik OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezpieczeństwo danych</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako zespół bezpieczeństwa chcę szyfrować dane i kontrolować dostęp, aby chronić dane osobowe i wrażliwe.</t>
   </si>
   <si>
     <t xml:space="preserve">• Szyfrowanie w transmisji i w spoczynku
@@ -1206,88 +1218,91 @@
 • Rejestrowanie zdarzeń bezpieczeństwa</t>
   </si>
   <si>
-    <t>NFR-5</t>
-  </si>
-  <si>
-    <t>US-N6</t>
-  </si>
-  <si>
-    <t>Responsywny interfejs (desktop + mobile)</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę korzystać z aplikacji na komputerze i telefonie, aby wpisywać nieobecności z dowolnego urządzenia.</t>
+    <t xml:space="preserve">NFR-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — dodatkowo bramka audytu zależności w CI (próg „high", podatności transitive domknięte przez pnpm.overrides) i zawężenie odczytu puli organizacji do ról raportowych (10.08.2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsywny interfejs (desktop + mobile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę korzystać z aplikacji na komputerze i telefonie, aby wpisywać nieobecności z dowolnego urządzenia.</t>
   </si>
   <si>
     <t xml:space="preserve">• Interfejs responsywny dla desktopu i urządzeń mobilnych
 • Kluczowe akcje dostępne na małym ekranie</t>
   </si>
   <si>
-    <t>NFR-6</t>
-  </si>
-  <si>
-    <t>Zrealizowane w wariancie uzgodnionym — pulpit i wpis mobilnie, pozostałe ekrany desktop; zawężenie zatwierdzone przez zamawiającego 10.08.2026</t>
-  </si>
-  <si>
-    <t>US-N7</t>
-  </si>
-  <si>
-    <t>Dostępność cyfrowa (WCAG 2.1 AA)</t>
-  </si>
-  <si>
-    <t>Jako pracownik z niepełnosprawnością chcę korzystać z aplikacji zgodnie z WCAG, aby mieć równy dostęp.</t>
-  </si>
-  <si>
-    <t>• Zgodność z WCAG 2.1 AA (kontrast, klawiatura, czytniki ekranu)</t>
-  </si>
-  <si>
-    <t>NFR-7</t>
-  </si>
-  <si>
-    <t>Zrealizowane — audyt axe 10.08.2026: 0 naruszeń na 12 ekranach; wyłączenie 1.4.10 Reflow zatwierdzone przez zamawiającego 10.08.2026</t>
-  </si>
-  <si>
-    <t>US-N8</t>
-  </si>
-  <si>
-    <t>Analityka adopcji</t>
-  </si>
-  <si>
-    <t>Jako właściciel produktu chcę mierzyć użycie i satysfakcję, aby weryfikować KPI &gt; 80% i wykrywać tarcia.</t>
+    <t xml:space="preserve">NFR-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane w wariancie uzgodnionym — pulpit i wpis mobilnie, pozostałe ekrany desktop; zawężenie zatwierdzone przez zamawiającego 10.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dostępność cyfrowa (WCAG 2.1 AA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik z niepełnosprawnością chcę korzystać z aplikacji zgodnie z WCAG, aby mieć równy dostęp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Zgodność z WCAG 2.1 AA (kontrast, klawiatura, czytniki ekranu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — audyt axe 10.08.2026: 0 naruszeń na 12 ekranach; wyłączenie 1.4.10 Reflow zatwierdzone przez zamawiającego 10.08.2026; lint reguł jsx-a11y wpięty do CI jako bramka statyczna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analityka adopcji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako właściciel produktu chcę mierzyć użycie i satysfakcję, aby weryfikować KPI &gt; 80% i wykrywać tarcia.</t>
   </si>
   <si>
     <t xml:space="preserve">• Pomiar użycia (kto wpisuje, gdzie tarcia)
 • Wskaźnik satysfakcji raportowany</t>
   </si>
   <si>
-    <t>NFR-8</t>
-  </si>
-  <si>
-    <t>US-N9</t>
-  </si>
-  <si>
-    <t>Lokalizacja PL/EN</t>
-  </si>
-  <si>
-    <t>Jako współpracownik OUT chcę korzystać z interfejsu w EN, aby zrozumieć aplikację bez znajomości PL.</t>
+    <t xml:space="preserve">NFR-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lokalizacja PL/EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako współpracownik OUT chcę korzystać z interfejsu w EN, aby zrozumieć aplikację bez znajomości PL.</t>
   </si>
   <si>
     <t xml:space="preserve">• Interfejs PL domyślnie
 • Opcjonalny EN (do potwierdzenia)</t>
   </si>
   <si>
-    <t>NFR-9</t>
-  </si>
-  <si>
-    <t>Niezrealizowane — potrzeba interfejsu EN nierozstrzygnięta u zamawiającego</t>
-  </si>
-  <si>
-    <t>US-B11</t>
-  </si>
-  <si>
-    <t>Nakładka L4 na zaplanowaną nieobecność</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę móc zapisać zwolnienie także na zaplanowanej nieobecności, aby choroba nie wymagała kasowania planu urlopu.</t>
+    <t xml:space="preserve">NFR-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niezrealizowane — potrzeba interfejsu EN nierozstrzygnięta u zamawiającego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-B11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakładka L4 na zaplanowaną nieobecność</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę móc zapisać zwolnienie także na zaplanowanej nieobecności, aby choroba nie wymagała kasowania planu urlopu.</t>
   </si>
   <si>
     <t xml:space="preserve">• Zapis chorobowego nie jest nigdy blokowany kolizją
@@ -1296,35 +1311,35 @@
 • Capacity obniża każdy z wpisów</t>
   </si>
   <si>
-    <t>FR-B5, FR-B10</t>
-  </si>
-  <si>
-    <t>Zrealizowane — zakres ponad backlog, dopisany 10.08.2026</t>
-  </si>
-  <si>
-    <t>US-C6</t>
-  </si>
-  <si>
-    <t>Wyszukiwarka osób w topbarze</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę szybko znaleźć osobę bez przechodzenia przez kalendarz, aby skrócić drogę do jej nieobecności.</t>
+    <t xml:space="preserve">FR-B5, FR-B10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zrealizowane — zakres ponad backlog, dopisany 10.08.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyszukiwarka osób w topbarze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę szybko znaleźć osobę bez przechodzenia przez kalendarz, aby skrócić drogę do jej nieobecności.</t>
   </si>
   <si>
     <t xml:space="preserve">• Wyszukiwanie po nazwisku w zasięgu widoczności użytkownika
 • Wynik prowadzi wprost do osoby</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>US-C7</t>
-  </si>
-  <si>
-    <t>Tryb ciemny interfejsu</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę móc przełączyć interfejs w tryb ciemny, aby dopasować go do ustawień stacji roboczej.</t>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-C7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tryb ciemny interfejsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę móc przełączyć interfejs w tryb ciemny, aby dopasować go do ustawień stacji roboczej.</t>
   </si>
   <si>
     <t xml:space="preserve">• Przełącznik w topbarze
@@ -1333,13 +1348,13 @@
 • Kontrast AA w obu motywach</t>
   </si>
   <si>
-    <t>US-E5</t>
-  </si>
-  <si>
-    <t>Powiadomienia w aplikacji (dzwonek)</t>
-  </si>
-  <si>
-    <t>Jako pracownik chcę widzieć istotne informacje po zalogowaniu, aby nie zależeć wyłącznie od poczty.</t>
+    <t xml:space="preserve">US-E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powiadomienia w aplikacji (dzwonek)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako pracownik chcę widzieć istotne informacje po zalogowaniu, aby nie zależeć wyłącznie od poczty.</t>
   </si>
   <si>
     <t xml:space="preserve">• Kanał w topbarze z licznikiem
@@ -1347,167 +1362,206 @@
 • Zamknięcie i obsługa z klawiatury</t>
   </si>
   <si>
-    <t>US-G8</t>
-  </si>
-  <si>
-    <t>Progi reguł administratora</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę ustawiać progi reguł (retencja, zaleganie, przypomnienia), aby nie zmieniać ich w kodzie.</t>
+    <t xml:space="preserve">US-G8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progi reguł administratora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę ustawiać progi reguł (retencja, zaleganie, przypomnienia), aby nie zmieniać ich w kodzie.</t>
   </si>
   <si>
     <t xml:space="preserve">• Okres retencji, próg zalegania i próg przypomnień edytowalne w panelu
 • Brak wpisu = wartość domyślna</t>
   </si>
   <si>
-    <t>FR-J2, FR-F5, FR-E3</t>
-  </si>
-  <si>
-    <t>US-I3</t>
-  </si>
-  <si>
-    <t>Ekran audytu i rejestru RODO</t>
-  </si>
-  <si>
-    <t>Jako administrator chcę przeglądać dziennik zdarzeń i rejestr czynności w aplikacji, aby nie sięgać do bazy.</t>
+    <t xml:space="preserve">FR-J2, FR-F5, FR-E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekran audytu i rejestru RODO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako administrator chcę przeglądać dziennik zdarzeń i rejestr czynności w aplikacji, aby nie sięgać do bazy.</t>
   </si>
   <si>
     <t xml:space="preserve">• Podgląd dziennika zmian i zdarzeń bezpieczeństwa
 • Podgląd rejestru czynności przetwarzania</t>
   </si>
   <si>
-    <t>FR-I1, FR-J3</t>
-  </si>
-  <si>
-    <t>Nazwa</t>
-  </si>
-  <si>
-    <t>Cel</t>
-  </si>
-  <si>
-    <t>Liczba historyjek</t>
-  </si>
-  <si>
-    <t>Suma story points</t>
-  </si>
-  <si>
-    <t>Historyjki MVP</t>
-  </si>
-  <si>
-    <t>RAZEM</t>
-  </si>
-  <si>
-    <t>Element</t>
-  </si>
-  <si>
-    <t>Znaczenie</t>
-  </si>
-  <si>
-    <t>Priorytet — Must</t>
-  </si>
-  <si>
-    <t>Konieczne w MVP (zakres minimalny).</t>
-  </si>
-  <si>
-    <t>Priorytet — Should</t>
-  </si>
-  <si>
-    <t>Ważne, planowane w Fazie 2.</t>
-  </si>
-  <si>
-    <t>Priorytet — Could</t>
-  </si>
-  <si>
-    <t>Opcjonalne, Faza 3 / docelowo.</t>
-  </si>
-  <si>
-    <t>Priorytet — Won't</t>
-  </si>
-  <si>
-    <t>Poza zakresem MVP.</t>
-  </si>
-  <si>
-    <t>Szacunek złożoności w skali Fibonacciego (1,2,3,5,8,13). Do kalibracji przez zespół.</t>
-  </si>
-  <si>
-    <t>Przypisanie do wdrożenia: MVP / Faza 2 / Faza 3 (wg Załącznika C dokumentu wymagań).</t>
-  </si>
-  <si>
-    <t>Odniesienie do wymagania w dokumencie „Wymagania funkcjonalne i niefunkcjonalne v2.0”.</t>
-  </si>
-  <si>
-    <t>Import do JIRA</t>
-  </si>
-  <si>
-    <t>Arkusz „Backlog”: kolumna „Typ zgłoszenia” = Epik/Historyjka; „Epik”/„Epik ID” służą do powiązania historyjek z epikami.</t>
-  </si>
-  <si>
-    <t>Stan wdrożenia — Zrealizowane</t>
-  </si>
-  <si>
-    <t>Funkcja działa w aplikacji; pokryta testami silnika lub suitą integracyjną.</t>
-  </si>
-  <si>
-    <t>Stan wdrożenia — wariant uzgodniony</t>
-  </si>
-  <si>
-    <t>Zakres zawężony w stosunku do pierwotnego brzmienia wymagania i zatwierdzony przez zamawiającego. Nie jest długiem ani odstępstwem do domknięcia.</t>
-  </si>
-  <si>
-    <t>Stan wdrożenia — Niezrealizowane</t>
-  </si>
-  <si>
-    <t>Nie zbudowane; powód podany w treści komórki.</t>
-  </si>
-  <si>
-    <t>Stan wdrożenia — zakres ponad backlog</t>
-  </si>
-  <si>
-    <t>Historyjka dopisana po fakcie: funkcja dostarczona, choć nie było jej w pierwotnym backlogu.</t>
-  </si>
-  <si>
-    <t>Aktualizacja stanu</t>
-  </si>
-  <si>
-    <t>Kolumna „Stan wdrożenia" odzwierciedla przegląd kodu i przebieg weryfikacji z 10.08.2026.</t>
+    <t xml:space="preserve">FR-I1, FR-J3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-N10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bramki jakości w potoku CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jako zespół utrzymania chcę, żeby potok CI sam zatrzymywał regresje dostępności, podatności zależności i niesprawdzony backup, aby jakość nie zależała od pamięci osoby wypuszczającej zmianę.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Lint reguł dostępności (jsx-a11y) uruchamiany w CI
+• Audyt zależności blokujący przy podatności „high"
+• Test odtworzenia backupu dostępny jako uruchamialny skrypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFR-4, NFR-5, NFR-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nazwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liczba historyjek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suma story points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historyjki MVP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAZEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Znaczenie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorytet — Must</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konieczne w MVP (zakres minimalny).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorytet — Should</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ważne, planowane w Fazie 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorytet — Could</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opcjonalne, Faza 3 / docelowo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorytet — Won't</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poza zakresem MVP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szacunek złożoności w skali Fibonacciego (1,2,3,5,8,13). Do kalibracji przez zespół.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Przypisanie do wdrożenia: MVP / Faza 2 / Faza 3 (wg Załącznika C dokumentu wymagań).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odniesienie do wymagania w dokumencie „Wymagania funkcjonalne i niefunkcjonalne v2.0”.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Import do JIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arkusz „Backlog”: kolumna „Typ zgłoszenia” = Epik/Historyjka; „Epik”/„Epik ID” służą do powiązania historyjek z epikami.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stan wdrożenia — Zrealizowane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funkcja działa w aplikacji; pokryta testami silnika lub suitą integracyjną.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stan wdrożenia — wariant uzgodniony</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zakres zawężony w stosunku do pierwotnego brzmienia wymagania i zatwierdzony przez zamawiającego. Nie jest długiem ani odstępstwem do domknięcia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stan wdrożenia — Niezrealizowane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nie zbudowane; powód podany w treści komórki.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stan wdrożenia — zakres ponad backlog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historyjka dopisana po fakcie: funkcja dostarczona, choć nie było jej w pierwotnym backlogu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aktualizacja stanu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kolumna „Stan wdrożenia" odzwierciedla przegląd kodu i przebieg weryfikacji z 10.08.2026.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="8">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <charset val="1"/>
-      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
-      <b/>
-      <charset val="1"/>
-      <color rgb="FF006A4E"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF006A4E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <charset val="1"/>
+      <b val="true"/>
       <sz val="9"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1549,14 +1603,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -1572,55 +1626,145 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF006A4E"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFF2F4F3"/>
+      <rgbColor rgb="FFE4F1EB"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFE8F0EC"/>
+      <rgbColor rgb="FFD7EAE0"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1800,23 +1944,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L85"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L86"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="46" customWidth="1"/>
-    <col min="7" max="7" width="52" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="46" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1854,7 +2001,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -1880,7 +2027,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1905,7 +2052,7 @@
       <c r="H3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J3" s="4" t="s">
@@ -1918,7 +2065,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -1943,7 +2090,7 @@
       <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J4" s="4" t="s">
@@ -1956,7 +2103,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
         <v>29</v>
       </c>
@@ -1981,7 +2128,7 @@
       <c r="H5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J5" s="4" t="s">
@@ -1994,7 +2141,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>36</v>
       </c>
@@ -2019,7 +2166,7 @@
       <c r="H6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="4" t="s">
@@ -2032,7 +2179,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
@@ -2057,7 +2204,7 @@
       <c r="H7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="4" t="s">
@@ -2070,7 +2217,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
@@ -2095,7 +2242,7 @@
       <c r="H8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J8" s="4" t="s">
@@ -2108,7 +2255,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>51</v>
       </c>
@@ -2133,7 +2280,7 @@
       <c r="H9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J9" s="4" t="s">
@@ -2146,7 +2293,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
         <v>56</v>
       </c>
@@ -2171,7 +2318,7 @@
       <c r="H10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="4" t="s">
@@ -2184,7 +2331,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
         <v>61</v>
       </c>
@@ -2209,7 +2356,7 @@
       <c r="H11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J11" s="4" t="s">
@@ -2222,7 +2369,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
@@ -2247,7 +2394,7 @@
       <c r="H12" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J12" s="4" t="s">
@@ -2260,7 +2407,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
         <v>73</v>
       </c>
@@ -2285,7 +2432,7 @@
       <c r="H13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J13" s="4" t="s">
@@ -2298,7 +2445,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>78</v>
       </c>
@@ -2324,7 +2471,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>81</v>
       </c>
@@ -2349,7 +2496,7 @@
       <c r="H15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J15" s="4" t="s">
@@ -2362,7 +2509,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>86</v>
       </c>
@@ -2387,7 +2534,7 @@
       <c r="H16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J16" s="4" t="s">
@@ -2400,7 +2547,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
         <v>91</v>
       </c>
@@ -2425,7 +2572,7 @@
       <c r="H17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -2438,7 +2585,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
         <v>96</v>
       </c>
@@ -2463,7 +2610,7 @@
       <c r="H18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -2476,7 +2623,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
         <v>101</v>
       </c>
@@ -2501,7 +2648,7 @@
       <c r="H19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J19" s="4" t="s">
@@ -2514,7 +2661,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>106</v>
       </c>
@@ -2539,7 +2686,7 @@
       <c r="H20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J20" s="4" t="s">
@@ -2552,7 +2699,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>111</v>
       </c>
@@ -2577,7 +2724,7 @@
       <c r="H21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J21" s="4" t="s">
@@ -2590,7 +2737,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
         <v>117</v>
       </c>
@@ -2615,7 +2762,7 @@
       <c r="H22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J22" s="4" t="s">
@@ -2628,7 +2775,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
         <v>122</v>
       </c>
@@ -2653,7 +2800,7 @@
       <c r="H23" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J23" s="4" t="s">
@@ -2666,7 +2813,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>127</v>
       </c>
@@ -2691,7 +2838,7 @@
       <c r="H24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -2704,7 +2851,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>132</v>
       </c>
@@ -2730,7 +2877,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>135</v>
       </c>
@@ -2755,7 +2902,7 @@
       <c r="H26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="4">
+      <c r="I26" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J26" s="4" t="s">
@@ -2768,7 +2915,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
         <v>140</v>
       </c>
@@ -2793,7 +2940,7 @@
       <c r="H27" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="4">
+      <c r="I27" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -2806,7 +2953,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
         <v>145</v>
       </c>
@@ -2831,7 +2978,7 @@
       <c r="H28" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="4">
+      <c r="I28" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J28" s="4" t="s">
@@ -2844,7 +2991,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>150</v>
       </c>
@@ -2869,7 +3016,7 @@
       <c r="H29" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J29" s="4" t="s">
@@ -2882,7 +3029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
         <v>155</v>
       </c>
@@ -2907,7 +3054,7 @@
       <c r="H30" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J30" s="4" t="s">
@@ -2920,7 +3067,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>160</v>
       </c>
@@ -2946,7 +3093,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
         <v>163</v>
       </c>
@@ -2971,7 +3118,7 @@
       <c r="H32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J32" s="4" t="s">
@@ -2984,7 +3131,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
         <v>168</v>
       </c>
@@ -3009,7 +3156,7 @@
       <c r="H33" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I33" s="4">
+      <c r="I33" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J33" s="4" t="s">
@@ -3022,7 +3169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>173</v>
       </c>
@@ -3047,7 +3194,7 @@
       <c r="H34" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I34" s="4">
+      <c r="I34" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J34" s="4" t="s">
@@ -3060,7 +3207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>178</v>
       </c>
@@ -3085,7 +3232,7 @@
       <c r="H35" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I35" s="4">
+      <c r="I35" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J35" s="4" t="s">
@@ -3098,7 +3245,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="36" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>184</v>
       </c>
@@ -3124,7 +3271,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>187</v>
       </c>
@@ -3149,7 +3296,7 @@
       <c r="H37" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I37" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J37" s="4" t="s">
@@ -3162,7 +3309,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>192</v>
       </c>
@@ -3187,7 +3334,7 @@
       <c r="H38" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I38" s="4">
+      <c r="I38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="4" t="s">
@@ -3200,7 +3347,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>197</v>
       </c>
@@ -3225,7 +3372,7 @@
       <c r="H39" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I39" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -3238,7 +3385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>202</v>
       </c>
@@ -3263,7 +3410,7 @@
       <c r="H40" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="4">
+      <c r="I40" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J40" s="4" t="s">
@@ -3276,7 +3423,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>207</v>
       </c>
@@ -3302,7 +3449,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>210</v>
       </c>
@@ -3327,7 +3474,7 @@
       <c r="H42" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I42" s="4">
+      <c r="I42" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J42" s="4" t="s">
@@ -3340,7 +3487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>215</v>
       </c>
@@ -3365,7 +3512,7 @@
       <c r="H43" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J43" s="4" t="s">
@@ -3378,7 +3525,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>220</v>
       </c>
@@ -3403,7 +3550,7 @@
       <c r="H44" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="4">
+      <c r="I44" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J44" s="4" t="s">
@@ -3416,7 +3563,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="45" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>225</v>
       </c>
@@ -3441,7 +3588,7 @@
       <c r="H45" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I45" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J45" s="4" t="s">
@@ -3454,7 +3601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>230</v>
       </c>
@@ -3479,7 +3626,7 @@
       <c r="H46" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I46" s="4">
+      <c r="I46" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J46" s="4" t="s">
@@ -3492,7 +3639,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>235</v>
       </c>
@@ -3517,7 +3664,7 @@
       <c r="H47" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I47" s="4">
+      <c r="I47" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J47" s="4" t="s">
@@ -3530,7 +3677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>240</v>
       </c>
@@ -3556,7 +3703,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>243</v>
       </c>
@@ -3581,7 +3728,7 @@
       <c r="H49" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I49" s="4">
+      <c r="I49" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J49" s="4" t="s">
@@ -3594,7 +3741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>248</v>
       </c>
@@ -3619,7 +3766,7 @@
       <c r="H50" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="4">
+      <c r="I50" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J50" s="4" t="s">
@@ -3632,7 +3779,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>253</v>
       </c>
@@ -3657,7 +3804,7 @@
       <c r="H51" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I51" s="4">
+      <c r="I51" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J51" s="4" t="s">
@@ -3670,7 +3817,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>258</v>
       </c>
@@ -3695,7 +3842,7 @@
       <c r="H52" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I52" s="4">
+      <c r="I52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J52" s="4" t="s">
@@ -3708,7 +3855,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>263</v>
       </c>
@@ -3733,7 +3880,7 @@
       <c r="H53" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I53" s="4">
+      <c r="I53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J53" s="4" t="s">
@@ -3746,7 +3893,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>268</v>
       </c>
@@ -3771,7 +3918,7 @@
       <c r="H54" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I54" s="4">
+      <c r="I54" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J54" s="4" t="s">
@@ -3784,7 +3931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>273</v>
       </c>
@@ -3809,7 +3956,7 @@
       <c r="H55" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I55" s="4">
+      <c r="I55" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J55" s="4" t="s">
@@ -3822,7 +3969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>278</v>
       </c>
@@ -3848,7 +3995,7 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>281</v>
       </c>
@@ -3873,7 +4020,7 @@
       <c r="H57" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I57" s="4">
+      <c r="I57" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J57" s="4" t="s">
@@ -3886,7 +4033,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>286</v>
       </c>
@@ -3911,7 +4058,7 @@
       <c r="H58" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I58" s="4">
+      <c r="I58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J58" s="4" t="s">
@@ -3924,7 +4071,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
         <v>291</v>
       </c>
@@ -3949,7 +4096,7 @@
       <c r="H59" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I59" s="4">
+      <c r="I59" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J59" s="4" t="s">
@@ -3962,7 +4109,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="60" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
         <v>296</v>
       </c>
@@ -3987,7 +4134,7 @@
       <c r="H60" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I60" s="4">
+      <c r="I60" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J60" s="4" t="s">
@@ -4000,7 +4147,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="61" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
         <v>301</v>
       </c>
@@ -4025,7 +4172,7 @@
       <c r="H61" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I61" s="4">
+      <c r="I61" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J61" s="4" t="s">
@@ -4038,7 +4185,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>307</v>
       </c>
@@ -4064,7 +4211,7 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
         <v>310</v>
       </c>
@@ -4089,7 +4236,7 @@
       <c r="H63" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I63" s="4">
+      <c r="I63" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J63" s="4" t="s">
@@ -4102,7 +4249,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
         <v>315</v>
       </c>
@@ -4127,7 +4274,7 @@
       <c r="H64" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I64" s="4">
+      <c r="I64" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J64" s="4" t="s">
@@ -4140,7 +4287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="65" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>320</v>
       </c>
@@ -4166,7 +4313,7 @@
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
         <v>323</v>
       </c>
@@ -4191,7 +4338,7 @@
       <c r="H66" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I66" s="4">
+      <c r="I66" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J66" s="4" t="s">
@@ -4201,12 +4348,12 @@
         <v>327</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>16</v>
@@ -4218,33 +4365,33 @@
         <v>321</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I67" s="4">
+      <c r="I67" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="68" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>16</v>
@@ -4256,33 +4403,33 @@
         <v>321</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I68" s="4">
+      <c r="I68" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="69" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>16</v>
@@ -4294,48 +4441,48 @@
         <v>321</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I69" s="4">
+      <c r="I69" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="70" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -4344,351 +4491,351 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I71" s="4">
+      <c r="I71" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="72" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I72" s="4">
+      <c r="I72" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="73" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I73" s="4">
+      <c r="I73" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="74" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I74" s="4">
+      <c r="I74" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="75" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I75" s="4">
+      <c r="I75" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I76" s="4">
+      <c r="I76" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="77" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I77" s="4">
+      <c r="I77" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="78" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I78" s="4">
+      <c r="I78" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="79" ht="23.85" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I79" s="4">
+      <c r="I79" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>71</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="80" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>16</v>
@@ -4700,33 +4847,33 @@
         <v>79</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I80" s="4" t="n">
         <v>5</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>21</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="81" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>16</v>
@@ -4738,33 +4885,33 @@
         <v>133</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I81" s="4">
+      <c r="I81" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>71</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="82" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>16</v>
@@ -4776,33 +4923,33 @@
         <v>133</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I82" s="4">
+      <c r="I82" s="4" t="n">
         <v>2</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>71</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="83" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>16</v>
@@ -4814,18 +4961,18 @@
         <v>185</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I83" s="4">
+      <c r="I83" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J83" s="4" t="s">
@@ -4835,12 +4982,12 @@
         <v>206</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="84" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>16</v>
@@ -4852,33 +4999,33 @@
         <v>241</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I84" s="4">
+      <c r="I84" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="85" ht="35.05" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>16</v>
@@ -4890,69 +5037,115 @@
         <v>308</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I85" s="4">
+      <c r="I85" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="2" ht="23.85" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -4962,20 +5155,20 @@
       <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4">
-        <f>COUNTIFS(Backlog!C:C,A2,Backlog!B:B,"Historyjka")</f>
+      <c r="D2" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A2,Backlog!B:B,"Historyjka")</f>
         <v>11</v>
       </c>
-      <c r="E2" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A2,Backlog!B:B,"Historyjka")</f>
+      <c r="E2" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A2,Backlog!B:B,"Historyjka")</f>
         <v>47</v>
       </c>
-      <c r="F2" s="4">
-        <f>COUNTIFS(Backlog!C:C,A2,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F2" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A2,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="23.85" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>78</v>
       </c>
@@ -4985,20 +5178,20 @@
       <c r="C3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="4">
-        <f>COUNTIFS(Backlog!C:C,A3,Backlog!B:B,"Historyjka")</f>
+      <c r="D3" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A3,Backlog!B:B,"Historyjka")</f>
         <v>11</v>
       </c>
-      <c r="E3" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A3,Backlog!B:B,"Historyjka")</f>
+      <c r="E3" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A3,Backlog!B:B,"Historyjka")</f>
         <v>53</v>
       </c>
-      <c r="F3" s="4">
-        <f>COUNTIFS(Backlog!C:C,A3,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F3" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A3,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>132</v>
       </c>
@@ -5008,20 +5201,20 @@
       <c r="C4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="4">
-        <f>COUNTIFS(Backlog!C:C,A4,Backlog!B:B,"Historyjka")</f>
+      <c r="D4" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A4,Backlog!B:B,"Historyjka")</f>
         <v>7</v>
       </c>
-      <c r="E4" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A4,Backlog!B:B,"Historyjka")</f>
+      <c r="E4" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A4,Backlog!B:B,"Historyjka")</f>
         <v>27</v>
       </c>
-      <c r="F4" s="4">
-        <f>COUNTIFS(Backlog!C:C,A4,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F4" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A4,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="23.85" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>160</v>
       </c>
@@ -5031,20 +5224,20 @@
       <c r="C5" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D5" s="4">
-        <f>COUNTIFS(Backlog!C:C,A5,Backlog!B:B,"Historyjka")</f>
+      <c r="D5" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A5,Backlog!B:B,"Historyjka")</f>
         <v>4</v>
       </c>
-      <c r="E5" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A5,Backlog!B:B,"Historyjka")</f>
+      <c r="E5" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A5,Backlog!B:B,"Historyjka")</f>
         <v>18</v>
       </c>
-      <c r="F5" s="4">
-        <f>COUNTIFS(Backlog!C:C,A5,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F5" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A5,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="23.85" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>184</v>
       </c>
@@ -5054,20 +5247,20 @@
       <c r="C6" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D6" s="4">
-        <f>COUNTIFS(Backlog!C:C,A6,Backlog!B:B,"Historyjka")</f>
+      <c r="D6" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A6,Backlog!B:B,"Historyjka")</f>
         <v>5</v>
       </c>
-      <c r="E6" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A6,Backlog!B:B,"Historyjka")</f>
+      <c r="E6" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A6,Backlog!B:B,"Historyjka")</f>
         <v>15</v>
       </c>
-      <c r="F6" s="4">
-        <f>COUNTIFS(Backlog!C:C,A6,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F6" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A6,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="23.85" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>207</v>
       </c>
@@ -5077,20 +5270,20 @@
       <c r="C7" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D7" s="4">
-        <f>COUNTIFS(Backlog!C:C,A7,Backlog!B:B,"Historyjka")</f>
+      <c r="D7" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A7,Backlog!B:B,"Historyjka")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A7,Backlog!B:B,"Historyjka")</f>
+      <c r="E7" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A7,Backlog!B:B,"Historyjka")</f>
         <v>31</v>
       </c>
-      <c r="F7" s="4">
-        <f>COUNTIFS(Backlog!C:C,A7,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F7" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A7,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>240</v>
       </c>
@@ -5100,20 +5293,20 @@
       <c r="C8" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D8" s="4">
-        <f>COUNTIFS(Backlog!C:C,A8,Backlog!B:B,"Historyjka")</f>
+      <c r="D8" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A8,Backlog!B:B,"Historyjka")</f>
         <v>8</v>
       </c>
-      <c r="E8" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A8,Backlog!B:B,"Historyjka")</f>
+      <c r="E8" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A8,Backlog!B:B,"Historyjka")</f>
         <v>40</v>
       </c>
-      <c r="F8" s="4">
-        <f>COUNTIFS(Backlog!C:C,A8,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F8" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A8,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="23.85" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>278</v>
       </c>
@@ -5123,20 +5316,20 @@
       <c r="C9" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D9" s="4">
-        <f>COUNTIFS(Backlog!C:C,A9,Backlog!B:B,"Historyjka")</f>
+      <c r="D9" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A9,Backlog!B:B,"Historyjka")</f>
         <v>5</v>
       </c>
-      <c r="E9" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A9,Backlog!B:B,"Historyjka")</f>
+      <c r="E9" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A9,Backlog!B:B,"Historyjka")</f>
         <v>25</v>
       </c>
-      <c r="F9" s="4">
-        <f>COUNTIFS(Backlog!C:C,A9,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F9" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A9,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>307</v>
       </c>
@@ -5146,20 +5339,20 @@
       <c r="C10" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D10" s="4">
-        <f>COUNTIFS(Backlog!C:C,A10,Backlog!B:B,"Historyjka")</f>
+      <c r="D10" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A10,Backlog!B:B,"Historyjka")</f>
         <v>3</v>
       </c>
-      <c r="E10" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A10,Backlog!B:B,"Historyjka")</f>
+      <c r="E10" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A10,Backlog!B:B,"Historyjka")</f>
         <v>11</v>
       </c>
-      <c r="F10" s="4">
-        <f>COUNTIFS(Backlog!C:C,A10,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="F10" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A10,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>320</v>
       </c>
@@ -5169,190 +5362,203 @@
       <c r="C11" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D11" s="4">
-        <f>COUNTIFS(Backlog!C:C,A11,Backlog!B:B,"Historyjka")</f>
+      <c r="D11" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A11,Backlog!B:B,"Historyjka")</f>
         <v>4</v>
       </c>
-      <c r="E11" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A11,Backlog!B:B,"Historyjka")</f>
-        <v>16</v>
-      </c>
-      <c r="F11" s="4">
-        <f>COUNTIFS(Backlog!C:C,A11,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+      <c r="E11" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A11,Backlog!B:B,"Historyjka")</f>
+        <v>16</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A11,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="12" ht="23.85" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D12" s="4">
-        <f>COUNTIFS(Backlog!C:C,A12,Backlog!B:B,"Historyjka")</f>
-        <v>9</v>
-      </c>
-      <c r="E12" s="4">
-        <f>SUMIFS(Backlog!I:I,Backlog!C:C,A12,Backlog!B:B,"Historyjka")</f>
-        <v>40</v>
-      </c>
-      <c r="F12" s="4">
-        <f>COUNTIFS(Backlog!C:C,A12,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
+        <v>346</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A12,Backlog!B:B,"Historyjka")</f>
+        <v>10</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <f aca="false">SUMIFS(Backlog!I:I,Backlog!C:C,A12,Backlog!B:B,"Historyjka")</f>
+        <v>43</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <f aca="false">COUNTIFS(Backlog!C:C,A12,Backlog!B:B,"Historyjka",Backlog!J:J,"MVP")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
-      <c r="D13" s="8">
-        <f>SUM(D2:D12)</f>
-        <v>73</v>
-      </c>
-      <c r="E13" s="8">
-        <f>SUM(E2:E12)</f>
-        <v>323</v>
-      </c>
-      <c r="F13" s="8">
-        <f>SUM(F2:F12)</f>
+      <c r="D13" s="8" t="n">
+        <f aca="false">SUM(D2:D12)</f>
+        <v>74</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <f aca="false">SUM(E2:E12)</f>
+        <v>326</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <f aca="false">SUM(F2:F12)</f>
         <v>41</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="80"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="9" ht="23.85" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>